--- a/سجل الايرادات والمصروفات.xlsx
+++ b/سجل الايرادات والمصروفات.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Henu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D060DF6C-BA32-42EE-A6F0-C3A5A82C0241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73ACC43-4511-4D84-90BB-0FFEB4741CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{B3249B00-A14B-4484-9177-C0A03E3FFFA3}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="88">
   <si>
     <t>هوستل الأهرامات — سجل حركة صندوق المصروفات النثرية</t>
   </si>
@@ -296,6 +296,15 @@
   </si>
   <si>
     <t xml:space="preserve">اخر دفعة من المرايات ل روماني </t>
+  </si>
+  <si>
+    <t>شراء معطر وملمع واكياس قمامة</t>
+  </si>
+  <si>
+    <t>بن</t>
+  </si>
+  <si>
+    <t>افطار غرفتين يومي 13 و14 اغسطس</t>
   </si>
 </sst>
 </file>
@@ -2890,7 +2899,9 @@
       <c r="N33" s="5"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="5"/>
+      <c r="A34" s="5">
+        <v>62</v>
+      </c>
       <c r="B34" s="8"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -3081,18 +3092,26 @@
       <c r="N4" s="12"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
-      <c r="B5" s="9"/>
+      <c r="A5" s="5">
+        <v>63</v>
+      </c>
+      <c r="B5" s="9">
+        <v>46247</v>
+      </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="10"/>
+      <c r="E5" s="10" t="s">
+        <v>85</v>
+      </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="G5" s="5">
+        <v>410</v>
+      </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5">
         <f t="shared" ref="J5:J34" si="1">J4-G5+H5</f>
-        <v>35211</v>
+        <v>34801</v>
       </c>
       <c r="K5" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3104,17 +3123,23 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
-      <c r="B6" s="9"/>
+      <c r="B6" s="9">
+        <v>46247</v>
+      </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>86</v>
+      </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="G6" s="5">
+        <v>85</v>
+      </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34716</v>
       </c>
       <c r="K6" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3129,14 +3154,18 @@
       <c r="B7" s="9"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="10"/>
+      <c r="E7" s="10" t="s">
+        <v>87</v>
+      </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="G7" s="5">
+        <v>200</v>
+      </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K7" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3158,7 +3187,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K8" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3180,7 +3209,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K9" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3202,7 +3231,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K10" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3224,7 +3253,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K11" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3246,7 +3275,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K12" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3268,7 +3297,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K13" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3290,7 +3319,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K14" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3312,7 +3341,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K15" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3334,7 +3363,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K16" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3356,7 +3385,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K17" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3378,7 +3407,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K18" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3400,7 +3429,7 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3421,7 +3450,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K20" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3443,7 +3472,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K21" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3465,7 +3494,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3487,7 +3516,7 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3509,7 +3538,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3531,7 +3560,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3553,7 +3582,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3575,7 +3604,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3597,7 +3626,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3619,7 +3648,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3641,7 +3670,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3663,7 +3692,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3685,7 +3714,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3707,7 +3736,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3729,7 +3758,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <f t="shared" si="1"/>
-        <v>35211</v>
+        <v>34516</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3750,7 +3779,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6">
         <f>SUM(G4:G34)</f>
-        <v>42809</v>
+        <v>43504</v>
       </c>
       <c r="H35" s="6">
         <f>SUM(H4:H34)</f>

--- a/سجل الايرادات والمصروفات.xlsx
+++ b/سجل الايرادات والمصروفات.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Henu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73ACC43-4511-4D84-90BB-0FFEB4741CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8734F39-2B2F-4842-AFC0-54E3148C3DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{B3249B00-A14B-4484-9177-C0A03E3FFFA3}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
   <si>
     <t>هوستل الأهرامات — سجل حركة صندوق المصروفات النثرية</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>افطار غرفتين يومي 13 و14 اغسطس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عهده مع منسي </t>
   </si>
 </sst>
 </file>
@@ -3180,14 +3183,18 @@
       <c r="B8" s="9"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="10"/>
+      <c r="E8" s="10" t="s">
+        <v>88</v>
+      </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="G8" s="5">
+        <v>1000</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K8" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3209,7 +3216,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K9" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3231,7 +3238,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K10" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3253,7 +3260,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K11" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3275,7 +3282,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K12" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3297,7 +3304,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K13" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3319,7 +3326,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K14" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3341,7 +3348,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K15" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3363,7 +3370,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K16" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3385,7 +3392,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K17" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3407,7 +3414,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K18" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3429,7 +3436,7 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3450,7 +3457,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K20" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3472,7 +3479,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K21" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3494,7 +3501,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3516,7 +3523,7 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3538,7 +3545,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3560,7 +3567,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3582,7 +3589,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3604,7 +3611,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3626,7 +3633,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3648,7 +3655,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3670,7 +3677,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3692,7 +3699,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3714,7 +3721,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3736,7 +3743,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3758,7 +3765,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>33516</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3779,7 +3786,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6">
         <f>SUM(G4:G34)</f>
-        <v>43504</v>
+        <v>44504</v>
       </c>
       <c r="H35" s="6">
         <f>SUM(H4:H34)</f>

--- a/سجل الايرادات والمصروفات.xlsx
+++ b/سجل الايرادات والمصروفات.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Henu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8734F39-2B2F-4842-AFC0-54E3148C3DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183D344B-20FD-4F59-B98C-440C16CA3365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{B3249B00-A14B-4484-9177-C0A03E3FFFA3}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="90">
   <si>
     <t>هوستل الأهرامات — سجل حركة صندوق المصروفات النثرية</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t xml:space="preserve">عهده مع منسي </t>
+  </si>
+  <si>
+    <t xml:space="preserve">توصيل المفروشات </t>
   </si>
 </sst>
 </file>
@@ -3154,7 +3157,9 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
-      <c r="B7" s="9"/>
+      <c r="B7" s="9">
+        <v>46248</v>
+      </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="10" t="s">
@@ -3180,7 +3185,9 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
-      <c r="B8" s="9"/>
+      <c r="B8" s="9">
+        <v>46248</v>
+      </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="10" t="s">
@@ -3206,17 +3213,23 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
-      <c r="B9" s="9"/>
+      <c r="B9" s="9">
+        <v>46248</v>
+      </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="10"/>
+      <c r="E9" s="10" t="s">
+        <v>89</v>
+      </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="G9" s="5">
+        <v>300</v>
+      </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K9" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3238,7 +3251,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K10" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3260,7 +3273,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K11" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3282,7 +3295,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K12" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3304,7 +3317,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K13" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3326,7 +3339,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K14" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3348,7 +3361,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K15" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3370,7 +3383,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K16" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3392,7 +3405,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K17" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3414,7 +3427,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K18" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3436,7 +3449,7 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3457,7 +3470,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K20" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3479,7 +3492,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K21" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3501,7 +3514,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3523,7 +3536,7 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3545,7 +3558,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3567,7 +3580,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3589,7 +3602,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3611,7 +3624,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3633,7 +3646,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3655,7 +3668,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3677,7 +3690,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3699,7 +3712,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3721,7 +3734,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3743,7 +3756,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3765,7 +3778,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>33216</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3786,7 +3799,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6">
         <f>SUM(G4:G34)</f>
-        <v>44504</v>
+        <v>44804</v>
       </c>
       <c r="H35" s="6">
         <f>SUM(H4:H34)</f>

--- a/سجل الايرادات والمصروفات.xlsx
+++ b/سجل الايرادات والمصروفات.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Henu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183D344B-20FD-4F59-B98C-440C16CA3365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5453363-A22A-432A-9A0E-98F405F2DFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{B3249B00-A14B-4484-9177-C0A03E3FFFA3}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
   <si>
     <t>هوستل الأهرامات — سجل حركة صندوق المصروفات النثرية</t>
   </si>
@@ -311,6 +311,21 @@
   </si>
   <si>
     <t xml:space="preserve">توصيل المفروشات </t>
+  </si>
+  <si>
+    <t xml:space="preserve">باقي حساب احمد كاميرات </t>
+  </si>
+  <si>
+    <t xml:space="preserve">تم تقفيل الحساب القديم </t>
+  </si>
+  <si>
+    <t xml:space="preserve">باقي مكافأة يوسف </t>
+  </si>
+  <si>
+    <t xml:space="preserve">مكافأة مبيت وعمل اضافي </t>
+  </si>
+  <si>
+    <t>كرتون ماء 5*130</t>
   </si>
 </sst>
 </file>
@@ -3223,13 +3238,13 @@
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>33166</v>
       </c>
       <c r="K9" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3241,45 +3256,61 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
-      <c r="B10" s="9"/>
+      <c r="B10" s="9">
+        <v>46248</v>
+      </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="10"/>
+      <c r="E10" s="10" t="s">
+        <v>90</v>
+      </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="G10" s="5">
+        <v>2500</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>30666</v>
       </c>
       <c r="K10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
-      <c r="L10" s="5"/>
+      <c r="L10" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
-      <c r="B11" s="9"/>
+      <c r="B11" s="9">
+        <v>46248</v>
+      </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="10"/>
+      <c r="E11" s="10" t="s">
+        <v>92</v>
+      </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="G11" s="5">
+        <v>1000</v>
+      </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29666</v>
       </c>
       <c r="K11" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
-      <c r="L11" s="5"/>
+      <c r="L11" s="5" t="s">
+        <v>93</v>
+      </c>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
     </row>
@@ -3288,14 +3319,18 @@
       <c r="B12" s="9"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="10"/>
+      <c r="E12" s="10" t="s">
+        <v>94</v>
+      </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="G12" s="5">
+        <v>650</v>
+      </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K12" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3317,7 +3352,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K13" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3339,7 +3374,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K14" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3361,7 +3396,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K15" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3383,7 +3418,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K16" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3405,7 +3440,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K17" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3427,7 +3462,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K18" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3449,7 +3484,7 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3470,7 +3505,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K20" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3492,7 +3527,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K21" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3514,7 +3549,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3536,7 +3571,7 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3558,7 +3593,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3580,7 +3615,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3602,7 +3637,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3624,7 +3659,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3646,7 +3681,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3668,7 +3703,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3690,7 +3725,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3712,7 +3747,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3734,7 +3769,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3756,7 +3791,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3778,7 +3813,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <f t="shared" si="1"/>
-        <v>33216</v>
+        <v>29016</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3799,7 +3834,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6">
         <f>SUM(G4:G34)</f>
-        <v>44804</v>
+        <v>49004</v>
       </c>
       <c r="H35" s="6">
         <f>SUM(H4:H34)</f>
